--- a/data/market_excel/market_final_한솔케미칼.xlsx
+++ b/data/market_excel/market_final_한솔케미칼.xlsx
@@ -533,26 +533,10 @@
           <t>AI 수요 확대에 따른 반도체 업황 호조로 산업 성장이 기대되나, OECD 경기선행지수 하락으로 거시 경제 불확실성이 존재합니다. 데이터 제한으로 인한 분석 한계도 있습니다. 따라서 현재로서는 '보유' 의견을 제시합니다.</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>소재</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -729,7 +713,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>소재</t>
+          <t>후공정/패키징/테스트</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -751,7 +735,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>한솔케미칼은 전자재료, 이차전지재료 및 다양한 화공약품을 포함한 폭넓은 제품 포트폴리오를 보유하고 있습니다. 특히, 반도체용 테이프와 같은 특수 소재에서 경쟁력을 갖추고 있습니다.</t>
+          <t>세계 유수의 반도체 업체들에게 최첨단 반도체 패키징 솔루션을 제공하여 업계에서 신뢰받는 기업으로 자리 잡고 있습니다.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -761,22 +745,22 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>사업보고서에 반도체용 테이프와 다양한 전자재료가 주요 제품으로 언급되었습니다.</t>
+          <t>사업 개요에서 반도체 조립 및 테스트 제품을 주력으로 생산하고 있다고 명시되어 있습니다.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>한솔케미칼</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>20241113000328</t>
+          <t>20241113000459</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-05-24T20:40:28.238730</t>
+          <t>2026-05-25T11:09:12.756789</t>
         </is>
       </c>
     </row>
@@ -950,19 +934,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>545.9</v>
+        <v>528.8</v>
       </c>
       <c r="D3" t="n">
-        <v>645.6</v>
+        <v>680.1</v>
       </c>
       <c r="E3" t="n">
-        <v>741.7</v>
+        <v>556.6</v>
       </c>
       <c r="F3" t="n">
-        <v>652</v>
+        <v>683.7</v>
       </c>
       <c r="G3" t="n">
-        <v>739.8</v>
+        <v>1913.6</v>
       </c>
     </row>
     <row r="4">
@@ -1175,7 +1159,7 @@
         <v>507.1</v>
       </c>
       <c r="F11" t="n">
-        <v>675.3</v>
+        <v>675</v>
       </c>
       <c r="G11" t="n">
         <v>807.1</v>
